--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_07/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_07/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999999935739</v>
+        <v>45.85402521435842</v>
       </c>
       <c r="B2" t="n">
-        <v>92.29166860741617</v>
+        <v>72.77877971798655</v>
       </c>
       <c r="C2" t="n">
-        <v>45.92646070653625</v>
+        <v>45.72961753363473</v>
       </c>
       <c r="D2" t="n">
-        <v>7.254345427475248</v>
+        <v>8.707857284869322</v>
       </c>
       <c r="E2" t="n">
-        <v>4.33922714549552</v>
+        <v>2.688695464336434</v>
       </c>
       <c r="F2" t="n">
-        <v>10.55377710265227</v>
+        <v>4.075739704689213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01227432435557308</v>
+        <v>0.1987865873025833</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9095301310836119</v>
+        <v>-0.003540843546782222</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9447491649320838</v>
+        <v>-0.5427882435421428</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9762072403020569</v>
+        <v>-0.4302158532863291</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.203227431127925e-05</v>
+        <v>-7.965021909209704e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069729892359</v>
+        <v>-0.555693501429056</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0003598252449872496</v>
+        <v>-0.02391257911650999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>44.05652684264814</v>
+        <v>99.99999983992829</v>
       </c>
       <c r="B3" t="n">
-        <v>83.15222345921241</v>
+        <v>107.9341200049958</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92817269145282</v>
+        <v>45.66457369332</v>
       </c>
       <c r="D3" t="n">
-        <v>8.945332565835491</v>
+        <v>8.057844335776174</v>
       </c>
       <c r="E3" t="n">
-        <v>4.679416693465779</v>
+        <v>2.558636366625277</v>
       </c>
       <c r="F3" t="n">
-        <v>3.898715426182167</v>
+        <v>10.74942682592584</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2371160932477766</v>
+        <v>0.01208013427305253</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01688555871815097</v>
+        <v>-0.8968309238567594</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.547416059675957</v>
+        <v>-0.9368371149844811</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.438843062834014</v>
+        <v>-0.9717314408089424</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.880560150476222e-05</v>
+        <v>-0.0003363058996186467</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5425380689542851</v>
+        <v>-0.587499998859489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0006069296406856948</v>
+        <v>-0.009045415615999697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56.54933975533583</v>
+        <v>45.85402521435842</v>
       </c>
       <c r="B4" t="n">
-        <v>91.82109607223028</v>
+        <v>72.97441969463947</v>
       </c>
       <c r="C4" t="n">
-        <v>45.93040269757139</v>
+        <v>45.72961753363473</v>
       </c>
       <c r="D4" t="n">
-        <v>7.180203977293822</v>
+        <v>8.707857284869322</v>
       </c>
       <c r="E4" t="n">
-        <v>4.623059349154829</v>
+        <v>2.690418231892481</v>
       </c>
       <c r="F4" t="n">
-        <v>5.175038743721587</v>
+        <v>4.075739704689213</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09112841589546196</v>
+        <v>0.1987865873025833</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5310185478631702</v>
+        <v>-0.003540843546782222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7560247005357958</v>
+        <v>-0.5427882435421428</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7902703140956927</v>
+        <v>-0.4302158532863291</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.002476729163731423</v>
+        <v>-7.965021909209704e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6254911210261754</v>
+        <v>-0.555693501429056</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0009288041554687811</v>
+        <v>-0.02391257911650999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54.70519852624376</v>
+        <v>80.76531855191124</v>
       </c>
       <c r="B5" t="n">
-        <v>93.22406177174494</v>
+        <v>74.66161185712977</v>
       </c>
       <c r="C5" t="n">
-        <v>45.92991013517072</v>
+        <v>45.64152789270588</v>
       </c>
       <c r="D5" t="n">
-        <v>7.528568906816764</v>
+        <v>10.70320577499006</v>
       </c>
       <c r="E5" t="n">
-        <v>4.669102010441222</v>
+        <v>2.16386507384361</v>
       </c>
       <c r="F5" t="n">
-        <v>4.976637018694338</v>
+        <v>7.906455628355668</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1033388306131067</v>
+        <v>0.0255380373535307</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4827205278009933</v>
+        <v>-0.810375382679665</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7355655804498679</v>
+        <v>-0.8879480630407528</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7610933351141443</v>
+        <v>-0.9368956512497076</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01823221316720025</v>
+        <v>-0.1094527519318316</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6132459089611302</v>
+        <v>-0.4807398891393343</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0008577087076148394</v>
+        <v>-0.003777804047058325</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68.15225155113423</v>
+        <v>89.42807943104761</v>
       </c>
       <c r="B6" t="n">
-        <v>108.5119976617204</v>
+        <v>111.5365561323775</v>
       </c>
       <c r="C6" t="n">
-        <v>45.96163660082787</v>
+        <v>45.65806203595591</v>
       </c>
       <c r="D6" t="n">
-        <v>12.20859983881394</v>
+        <v>9.61163734351873</v>
       </c>
       <c r="E6" t="n">
-        <v>4.560783117190375</v>
+        <v>2.538292602282607</v>
       </c>
       <c r="F6" t="n">
-        <v>6.363406713104238</v>
+        <v>9.117209830268891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04861153478067794</v>
+        <v>0.01777559679662975</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7250197456252595</v>
+        <v>-0.8577124859085504</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8431252171502275</v>
+        <v>-0.9136012884218352</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.896287541213301</v>
+        <v>-0.956755297539552</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.09650258279922533</v>
+        <v>-0.01447006075857372</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3841020713394088</v>
+        <v>-0.5121750659462141</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.004826838250663115</v>
+        <v>-0.007557036789923588</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86.01918340439127</v>
+        <v>47.20226674055098</v>
       </c>
       <c r="B7" t="n">
-        <v>79.59967369610247</v>
+        <v>71.70205801578696</v>
       </c>
       <c r="C7" t="n">
-        <v>46.54017776319313</v>
+        <v>45.6319913934985</v>
       </c>
       <c r="D7" t="n">
-        <v>9.357563182602139</v>
+        <v>8.701887503482975</v>
       </c>
       <c r="E7" t="n">
-        <v>2.779356664311086</v>
+        <v>2.304294898067581</v>
       </c>
       <c r="F7" t="n">
-        <v>8.488693700099567</v>
+        <v>4.229359253389661</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02073843369725586</v>
+        <v>0.1779027595762366</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8606299087164638</v>
+        <v>-0.08566709192881036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9153291242352269</v>
+        <v>-0.5746166504306195</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9578764050415244</v>
+        <v>-0.4918030644428559</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.001199074984677457</v>
+        <v>-0.037634866535813</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5175692981433314</v>
+        <v>-0.5646817782703399</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03246986735175689</v>
+        <v>-0.001598032799655924</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56.99254553207025</v>
+        <v>60.91505329568497</v>
       </c>
       <c r="B8" t="n">
-        <v>95.36354320407368</v>
+        <v>175.7790760976482</v>
       </c>
       <c r="C8" t="n">
-        <v>45.9300288853246</v>
+        <v>45.63286709814854</v>
       </c>
       <c r="D8" t="n">
-        <v>7.588531378848584</v>
+        <v>12.73859866525703</v>
       </c>
       <c r="E8" t="n">
-        <v>4.630629419296961</v>
+        <v>2.517099295917809</v>
       </c>
       <c r="F8" t="n">
-        <v>5.305248661765745</v>
+        <v>5.589874921052562</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08865575773879791</v>
+        <v>0.07248531170637687</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5415158356721571</v>
+        <v>-0.5618570476925698</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.760485388076747</v>
+        <v>-0.7671539393736743</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7964573099430844</v>
+        <v>-0.8077156663288487</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1243643487572931</v>
+        <v>-0.002832942719244244</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6284340348545474</v>
+        <v>-0.3090197547317555</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0008748488615561285</v>
+        <v>-0.001798193862524444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90.70256683919177</v>
+        <v>85.73999287682436</v>
       </c>
       <c r="B9" t="n">
-        <v>87.22695673970541</v>
+        <v>66.56662098461025</v>
       </c>
       <c r="C9" t="n">
-        <v>45.93113322595761</v>
+        <v>45.67082615963881</v>
       </c>
       <c r="D9" t="n">
-        <v>9.397916422784395</v>
+        <v>9.610844948659549</v>
       </c>
       <c r="E9" t="n">
-        <v>4.378421640521893</v>
+        <v>2.922006121729389</v>
       </c>
       <c r="F9" t="n">
-        <v>9.249186116101848</v>
+        <v>8.508647557054624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01724043179354896</v>
+        <v>0.02058243631870453</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8803155129922501</v>
+        <v>-0.8405801295172847</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9268417098103543</v>
+        <v>-0.9045037906979457</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9655566989541783</v>
+        <v>-0.9498477600304902</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1331109272266438</v>
+        <v>-0.03661467319776797</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5525544989733387</v>
+        <v>-0.2846003086709448</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.00103424712618129</v>
+        <v>-0.01047455077458667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84.33160115091704</v>
+        <v>64.36085355715174</v>
       </c>
       <c r="B10" t="n">
-        <v>96.37400456463671</v>
+        <v>97.18599828122551</v>
       </c>
       <c r="C10" t="n">
-        <v>45.92398798493404</v>
+        <v>45.63415904479304</v>
       </c>
       <c r="D10" t="n">
-        <v>10.3734234024256</v>
+        <v>12.10541459678034</v>
       </c>
       <c r="E10" t="n">
-        <v>2.548733483724044</v>
+        <v>4.277450339573581</v>
       </c>
       <c r="F10" t="n">
-        <v>8.366776775643947</v>
+        <v>5.892757619347992</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0223209805953486</v>
+        <v>0.05879017846710727</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8523015302849299</v>
+        <v>-0.6315583772829785</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.910491272268608</v>
+        <v>-0.7998205748567062</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9545036060210472</v>
+        <v>-0.8477451891760466</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1357425777207383</v>
+        <v>-0.01165031844216347</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5049629410348691</v>
+        <v>-0.3577064016786381</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.917674521219863e-06</v>
+        <v>-0.002093495952695673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>44.48338845812291</v>
+        <v>49.72407152783656</v>
       </c>
       <c r="B11" t="n">
-        <v>109.3203248155041</v>
+        <v>68.32357739933389</v>
       </c>
       <c r="C11" t="n">
-        <v>45.96811937782937</v>
+        <v>45.63053898793047</v>
       </c>
       <c r="D11" t="n">
-        <v>8.945751292785568</v>
+        <v>8.19848935098241</v>
       </c>
       <c r="E11" t="n">
-        <v>3.494542386520277</v>
+        <v>4.383793924896233</v>
       </c>
       <c r="F11" t="n">
-        <v>3.947214904087708</v>
+        <v>4.453779491821845</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2284935746154245</v>
+        <v>0.1455509950465016</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04461942963093631</v>
+        <v>-0.21664658575868</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5581262275930058</v>
+        <v>-0.6270147770107565</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4597976129921965</v>
+        <v>-0.5862714632860819</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01320776995414667</v>
+        <v>-0.002626864518850214</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5453724565388466</v>
+        <v>-0.5814938101855771</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.005583802683695305</v>
+        <v>-0.001266054384107262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66.72488818455983</v>
+        <v>53.21482466846071</v>
       </c>
       <c r="B12" t="n">
-        <v>108.8918776588828</v>
+        <v>93.21026579077028</v>
       </c>
       <c r="C12" t="n">
-        <v>45.93734881394236</v>
+        <v>45.6355812838497</v>
       </c>
       <c r="D12" t="n">
-        <v>12.31944729636738</v>
+        <v>8.188957770615566</v>
       </c>
       <c r="E12" t="n">
-        <v>2.469484967832142</v>
+        <v>2.19106173443802</v>
       </c>
       <c r="F12" t="n">
-        <v>6.200539758173718</v>
+        <v>4.903915155465012</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05259643913076641</v>
+        <v>0.1125860324117849</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7073890787166428</v>
+        <v>-0.3566804498880496</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8344659585334843</v>
+        <v>-0.6842291735759336</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8873703816064641</v>
+        <v>-0.6811570251668867</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.08792624239778131</v>
+        <v>-0.02899198885054852</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3734395674611356</v>
+        <v>-0.5870272229002511</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.001931392362698124</v>
+        <v>-0.00241857916564503</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>71.00843960877926</v>
+        <v>48.22164200184053</v>
       </c>
       <c r="B13" t="n">
-        <v>108.7376414172587</v>
+        <v>69.04783791051837</v>
       </c>
       <c r="C13" t="n">
-        <v>45.92448135489429</v>
+        <v>45.6362848805153</v>
       </c>
       <c r="D13" t="n">
-        <v>11.32334060380733</v>
+        <v>8.469192729051045</v>
       </c>
       <c r="E13" t="n">
-        <v>2.301250448082908</v>
+        <v>2.817110288101309</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5874245947827</v>
+        <v>4.313500754766691</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04159186401004293</v>
+        <v>0.1637873539041661</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7564185023485819</v>
+        <v>-0.1419352634298372</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8589798696879687</v>
+        <v>-0.5968758209952959</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9117224833436838</v>
+        <v>-0.5329816831956947</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.006673790173361518</v>
+        <v>-0.01702478087145253</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4054379952918401</v>
+        <v>-0.5714776133456037</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.412968386965498e-05</v>
+        <v>-0.002579401260639769</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94.64620212650198</v>
+        <v>92.64675608398225</v>
       </c>
       <c r="B14" t="n">
-        <v>67.84374747895149</v>
+        <v>100.6680894591599</v>
       </c>
       <c r="C14" t="n">
-        <v>46.1141618163482</v>
+        <v>45.66457540254375</v>
       </c>
       <c r="D14" t="n">
-        <v>8.679325096814328</v>
+        <v>9.140875518766741</v>
       </c>
       <c r="E14" t="n">
-        <v>4.414789926348856</v>
+        <v>2.007267432896192</v>
       </c>
       <c r="F14" t="n">
-        <v>9.82004750105957</v>
+        <v>9.592375213754522</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01485778636113893</v>
+        <v>0.01570793942181105</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8940880771885694</v>
+        <v>-0.8715270453546489</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9351573608696061</v>
+        <v>-0.9216415597336626</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9706974809181868</v>
+        <v>-0.962221933017013</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1219508657709048</v>
+        <v>-0.005758132248065958</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5820137295589995</v>
+        <v>-0.5351081370983736</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.01622434317112999</v>
+        <v>-0.009045806295713138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>53.62199883025007</v>
+        <v>51.50227265642469</v>
       </c>
       <c r="B15" t="n">
-        <v>81.40790463208447</v>
+        <v>66.45387141952172</v>
       </c>
       <c r="C15" t="n">
-        <v>45.93573167326664</v>
+        <v>45.63190698828592</v>
       </c>
       <c r="D15" t="n">
-        <v>7.642654068261042</v>
+        <v>8.554751839828819</v>
       </c>
       <c r="E15" t="n">
-        <v>4.730890199569354</v>
+        <v>2.660888670322401</v>
       </c>
       <c r="F15" t="n">
-        <v>4.849269639636543</v>
+        <v>4.738540515772463</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1114693385748936</v>
+        <v>0.1276024898959632</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4512239991043303</v>
+        <v>-0.2938934141240406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7225077773601337</v>
+        <v>-0.6588969550179796</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7415739537523388</v>
+        <v>-0.6395720388899481</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.005058759799567149</v>
+        <v>-0.09935616193482681</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6060533958406654</v>
+        <v>-0.5847647722667604</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.001697977590426796</v>
+        <v>-0.001578740179638827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>74.52782879710873</v>
+        <v>65.52829143012579</v>
       </c>
       <c r="B16" t="n">
-        <v>128.2490475721308</v>
+        <v>175.7790760976482</v>
       </c>
       <c r="C16" t="n">
-        <v>46.18126142231635</v>
+        <v>45.63194363046212</v>
       </c>
       <c r="D16" t="n">
-        <v>11.23915512624308</v>
+        <v>12.73859866525703</v>
       </c>
       <c r="E16" t="n">
-        <v>4.979527330341602</v>
+        <v>2.660657876445968</v>
       </c>
       <c r="F16" t="n">
-        <v>7.063092932611312</v>
+        <v>6.13959236724714</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03487612663366269</v>
+        <v>0.05521521273379951</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7884634201555837</v>
+        <v>-0.6466085680221197</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8755415347837129</v>
+        <v>-0.8054211645641272</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9267755517673499</v>
+        <v>-0.8554667940281402</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.06874312383225648</v>
+        <v>-0.07328761940628771</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4317280779354594</v>
+        <v>-0.3418890764396462</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.02017410194167948</v>
+        <v>-0.001587115534198574</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>50.34074185795892</v>
+        <v>55.14495398862793</v>
       </c>
       <c r="B17" t="n">
-        <v>81.12654034653582</v>
+        <v>95.63967644486696</v>
       </c>
       <c r="C17" t="n">
-        <v>45.92771060659127</v>
+        <v>45.66828006664078</v>
       </c>
       <c r="D17" t="n">
-        <v>8.130667404997597</v>
+        <v>8.209103422145494</v>
       </c>
       <c r="E17" t="n">
-        <v>4.612588510976087</v>
+        <v>3.012503002150133</v>
       </c>
       <c r="F17" t="n">
-        <v>4.504125276891064</v>
+        <v>5.171014798890069</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1418475710849148</v>
+        <v>0.09847489884825186</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3383618458229153</v>
+        <v>-0.4209580412577698</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6765403227481538</v>
+        <v>-0.7099099896512001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6686282783391582</v>
+        <v>-0.7227705110771463</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.007211041135198463</v>
+        <v>-0.09720026285024438</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5842656461652271</v>
+        <v>-0.5992513752613102</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0005402332583931246</v>
+        <v>-0.009892586660750213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89.25652021164727</v>
+        <v>50.31993931850636</v>
       </c>
       <c r="B18" t="n">
-        <v>98.60785429890136</v>
+        <v>69.04783791051837</v>
       </c>
       <c r="C18" t="n">
-        <v>46.21675180604306</v>
+        <v>45.6362848805153</v>
       </c>
       <c r="D18" t="n">
-        <v>9.007432602042</v>
+        <v>8.469192729051045</v>
       </c>
       <c r="E18" t="n">
-        <v>4.369959530305975</v>
+        <v>2.735808554487212</v>
       </c>
       <c r="F18" t="n">
-        <v>8.950477043804657</v>
+        <v>4.573335016458587</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01820199172855612</v>
+        <v>0.1392908691470757</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8747168131215359</v>
+        <v>-0.2436757986332724</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9235558009704877</v>
+        <v>-0.6380611738751351</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.963415147503593</v>
+        <v>-0.6051169103341215</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01669317159595263</v>
+        <v>-0.04407560101348172</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5417524298328363</v>
+        <v>-0.5770796055702914</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.02138993243730798</v>
+        <v>-0.002579401260639769</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>49.38847450010921</v>
+        <v>50.90489858923195</v>
       </c>
       <c r="B19" t="n">
-        <v>83.61887305737798</v>
+        <v>68.16658837018421</v>
       </c>
       <c r="C19" t="n">
-        <v>45.92991776172484</v>
+        <v>45.6340331453988</v>
       </c>
       <c r="D19" t="n">
-        <v>8.705898822055079</v>
+        <v>8.228529294852844</v>
       </c>
       <c r="E19" t="n">
-        <v>4.613252631427568</v>
+        <v>2.190738069863213</v>
       </c>
       <c r="F19" t="n">
-        <v>4.480739435355193</v>
+        <v>4.608138073403954</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1529436980036052</v>
+        <v>0.1331698854955337</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2995040118871599</v>
+        <v>-0.2692271077000855</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.660579774914561</v>
+        <v>-0.6486432932282359</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6424530513416891</v>
+        <v>-0.6227667519528782</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.10521881494944</v>
+        <v>-0.006829947274458574</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5779425318855086</v>
+        <v>-0.5808818408300076</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.000858809508814042</v>
+        <v>-0.002064718948297239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>52.47457737478494</v>
+        <v>69.71449985184232</v>
       </c>
       <c r="B20" t="n">
-        <v>106.1900168556884</v>
+        <v>94.30067415164818</v>
       </c>
       <c r="C20" t="n">
-        <v>45.92454269497839</v>
+        <v>45.65806203595591</v>
       </c>
       <c r="D20" t="n">
-        <v>7.875040445627137</v>
+        <v>11.97103447332021</v>
       </c>
       <c r="E20" t="n">
-        <v>2.439357629982458</v>
+        <v>2.169987693651778</v>
       </c>
       <c r="F20" t="n">
-        <v>4.735485413095829</v>
+        <v>6.548214410022079</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1210699288171108</v>
+        <v>0.04374313211881947</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4149084726878147</v>
+        <v>-0.7056722648066369</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7076805160519725</v>
+        <v>-0.8335965746488597</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7185943216839837</v>
+        <v>-0.8866491336046316</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02034116698438133</v>
+        <v>-0.0238790865530681</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5984344462567061</v>
+        <v>-0.3717158114443765</v>
       </c>
       <c r="M20" t="n">
-        <v>-8.298338594799245e-05</v>
+        <v>-0.007557036789923588</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46.5200480747944</v>
+        <v>56.66808403960412</v>
       </c>
       <c r="B21" t="n">
-        <v>82.8560948357286</v>
+        <v>99.3038051436324</v>
       </c>
       <c r="C21" t="n">
-        <v>45.92848024301225</v>
+        <v>45.63404793994376</v>
       </c>
       <c r="D21" t="n">
-        <v>8.94046436923318</v>
+        <v>8.057981554468096</v>
       </c>
       <c r="E21" t="n">
-        <v>2.633092969696345</v>
+        <v>2.053256387343695</v>
       </c>
       <c r="F21" t="n">
-        <v>4.176266088313607</v>
+        <v>5.359189033384028</v>
       </c>
       <c r="G21" t="n">
-        <v>0.192417173809229</v>
+        <v>0.08886080975727358</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1634512048390271</v>
+        <v>-0.4657852180373445</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6049853605020552</v>
+        <v>-0.7282983250295828</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5472654761115725</v>
+        <v>-0.7509214283802362</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.06943797781513789</v>
+        <v>-0.1138138828012035</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5588960026301262</v>
+        <v>-0.6088978655841595</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0006513210027272</v>
+        <v>-0.002068100558574176</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>50.67752654633722</v>
+        <v>95.8253823107755</v>
       </c>
       <c r="B22" t="n">
-        <v>68.14369294752441</v>
+        <v>160.0793508129836</v>
       </c>
       <c r="C22" t="n">
-        <v>45.96580919089014</v>
+        <v>45.63371631400627</v>
       </c>
       <c r="D22" t="n">
-        <v>8.045589212680127</v>
+        <v>9.146567711147645</v>
       </c>
       <c r="E22" t="n">
-        <v>4.183808586439549</v>
+        <v>2.023549535543858</v>
       </c>
       <c r="F22" t="n">
-        <v>4.607922601863996</v>
+        <v>10.15691678767192</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1379576456745927</v>
+        <v>0.01399925153423361</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3516072962154314</v>
+        <v>-0.8833631129472292</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6820068158413138</v>
+        <v>-0.9286396068139463</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.677473913213585</v>
+        <v>-0.96675095419999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.08836972300923852</v>
+        <v>-0.1001399396964961</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6014371750410668</v>
+        <v>-0.5577558489642753</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.005314052645054785</v>
+        <v>-0.00199230034429107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>44.90697313043726</v>
+        <v>83.55884957792104</v>
       </c>
       <c r="B23" t="n">
-        <v>76.591216231012</v>
+        <v>83.91457496467854</v>
       </c>
       <c r="C23" t="n">
-        <v>45.92490320715493</v>
+        <v>45.66377887693324</v>
       </c>
       <c r="D23" t="n">
-        <v>8.667257232984781</v>
+        <v>10.4740316192647</v>
       </c>
       <c r="E23" t="n">
-        <v>3.748765450432159</v>
+        <v>2.679305045190763</v>
       </c>
       <c r="F23" t="n">
-        <v>3.985742599430216</v>
+        <v>8.302278545702109</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2196508904699921</v>
+        <v>0.02261811126880602</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0716832813776585</v>
+        <v>-0.8267292850172483</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5687553061740898</v>
+        <v>-0.8961328563726997</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4801649599267489</v>
+        <v>-0.9438637235801841</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0151162328194743</v>
+        <v>-0.03776802538914607</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5594913203481843</v>
+        <v>-0.4703568032426874</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0001350189749668644</v>
+        <v>-0.008863743299025589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96.92547683088766</v>
+        <v>56.1520298524628</v>
       </c>
       <c r="B24" t="n">
-        <v>85.05832479272588</v>
+        <v>102.3084336754863</v>
       </c>
       <c r="C24" t="n">
-        <v>45.9275401595616</v>
+        <v>45.63361444187862</v>
       </c>
       <c r="D24" t="n">
-        <v>8.130667404997597</v>
+        <v>7.71544975922729</v>
       </c>
       <c r="E24" t="n">
-        <v>2.795699496470834</v>
+        <v>2.461556323838549</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1321089372376</v>
+        <v>5.229741954690271</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01367513830710449</v>
+        <v>0.09182626014466559</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9010764147839431</v>
+        <v>-0.4513370448512941</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9394633630567653</v>
+        <v>-0.7223823936504212</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9732259982504095</v>
+        <v>-0.7419596610789272</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.08422901787536574</v>
+        <v>-0.01448953845761853</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5990400705344496</v>
+        <v>-0.605629522398931</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0005156312833074504</v>
+        <v>-0.001969015286542447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>62.71979270911977</v>
+        <v>79.19522838404832</v>
       </c>
       <c r="B25" t="n">
-        <v>103.7845304570018</v>
+        <v>97.33854596536733</v>
       </c>
       <c r="C25" t="n">
-        <v>45.93734881394236</v>
+        <v>45.63190698828592</v>
       </c>
       <c r="D25" t="n">
-        <v>12.31944729636738</v>
+        <v>10.968044447763</v>
       </c>
       <c r="E25" t="n">
-        <v>2.469484967832142</v>
+        <v>2.006011250084963</v>
       </c>
       <c r="F25" t="n">
-        <v>5.79096304674774</v>
+        <v>7.712885619637624</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06596729779703364</v>
+        <v>0.02742292318884478</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6493569309469969</v>
+        <v>-0.7974296638899606</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8069570943853357</v>
+        <v>-0.8802539985503951</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8568428875602001</v>
+        <v>-0.9309504909599235</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.07149524730108414</v>
+        <v>-0.0320126742654505</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3651866572149007</v>
+        <v>-0.4392660022363443</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.001931392362698124</v>
+        <v>-0.001578740179638827</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>45.25769222526929</v>
+        <v>54.4443636811404</v>
       </c>
       <c r="B26" t="n">
-        <v>83.15222345921241</v>
+        <v>94.24874921879633</v>
       </c>
       <c r="C26" t="n">
-        <v>45.92817269145282</v>
+        <v>45.66471980463041</v>
       </c>
       <c r="D26" t="n">
-        <v>8.945332565835491</v>
+        <v>7.962520141941325</v>
       </c>
       <c r="E26" t="n">
-        <v>4.679416693465779</v>
+        <v>2.326892990729185</v>
       </c>
       <c r="F26" t="n">
-        <v>4.032539551470525</v>
+        <v>5.033891927951828</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2138276683568603</v>
+        <v>0.1032115829062921</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.09232336612673579</v>
+        <v>-0.3988073137242198</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5767450092500537</v>
+        <v>-0.7010124770178833</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4953726351914461</v>
+        <v>-0.7086147371890156</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.03438302572007342</v>
+        <v>-0.0162172890473485</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5505138815457257</v>
+        <v>-0.5948143033138893</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0006069296406856948</v>
+        <v>-0.009078812486951054</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>59.78706763208131</v>
+        <v>87.13751489622516</v>
       </c>
       <c r="B27" t="n">
-        <v>94.79758836375618</v>
+        <v>72.2115476990251</v>
       </c>
       <c r="C27" t="n">
-        <v>45.93067183648028</v>
+        <v>45.66379682343107</v>
       </c>
       <c r="D27" t="n">
-        <v>7.169108194434308</v>
+        <v>10.82744908744044</v>
       </c>
       <c r="E27" t="n">
-        <v>4.098419319267542</v>
+        <v>2.714469012291182</v>
       </c>
       <c r="F27" t="n">
-        <v>5.643071288483483</v>
+        <v>8.936104252089969</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07405529767802704</v>
+        <v>0.01955180509547916</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6018754882151536</v>
+        <v>-0.846455011580615</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7870083081510101</v>
+        <v>-0.9070936979908629</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8312531232135976</v>
+        <v>-0.9521556714421205</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1432028613618325</v>
+        <v>-0.1748585426813088</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6469898348091624</v>
+        <v>-0.4958547936356041</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0009676511142221659</v>
+        <v>-0.008867845355672865</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51.6021746850736</v>
+        <v>74.09072182504106</v>
       </c>
       <c r="B28" t="n">
-        <v>88.97975546387889</v>
+        <v>158.8756373140636</v>
       </c>
       <c r="C28" t="n">
-        <v>45.96164801158209</v>
+        <v>45.63504995648469</v>
       </c>
       <c r="D28" t="n">
-        <v>8.018775728497097</v>
+        <v>11.38676796581935</v>
       </c>
       <c r="E28" t="n">
-        <v>2.439357629982458</v>
+        <v>2.357137771273627</v>
       </c>
       <c r="F28" t="n">
-        <v>4.647033145501784</v>
+        <v>7.044359267446966</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1290816441568214</v>
+        <v>0.03492391967305079</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3851101969185926</v>
+        <v>-0.7538907561842118</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.695554465731078</v>
+        <v>-0.8576145309430163</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6993822018588288</v>
+        <v>-0.91061296177855</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.02488449071265271</v>
+        <v>-0.00439751548904508</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5926416383236117</v>
+        <v>-0.4028963930034175</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.004828170632619816</v>
+        <v>-0.002297132910786676</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>78.4728832573102</v>
+        <v>46.95143209938666</v>
       </c>
       <c r="B29" t="n">
-        <v>119.5879855040237</v>
+        <v>70.6385771167464</v>
       </c>
       <c r="C29" t="n">
-        <v>45.95665763775703</v>
+        <v>45.63806920114523</v>
       </c>
       <c r="D29" t="n">
-        <v>11.06258291329167</v>
+        <v>8.686201402471132</v>
       </c>
       <c r="E29" t="n">
-        <v>4.062528821898521</v>
+        <v>2.777309107493101</v>
       </c>
       <c r="F29" t="n">
-        <v>7.589533098758588</v>
+        <v>4.197294462395505</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02892628652044045</v>
+        <v>0.1815494525090513</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8179598301861724</v>
+        <v>-0.07110803401517053</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8913319341817204</v>
+        <v>-0.5689236620581334</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9399885545375228</v>
+        <v>-0.4810161305312609</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1171923273151955</v>
+        <v>-0.02661183609750413</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.4611979098415767</v>
+        <v>-0.5630095473292445</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.004245467341695371</v>
+        <v>-0.002987245976051739</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>48.53783766707834</v>
+        <v>59.12200758007931</v>
       </c>
       <c r="B30" t="n">
-        <v>88.92343062624286</v>
+        <v>163.2311148534781</v>
       </c>
       <c r="C30" t="n">
-        <v>45.95474982949233</v>
+        <v>45.64645941868344</v>
       </c>
       <c r="D30" t="n">
-        <v>8.377909312968214</v>
+        <v>12.89670012733087</v>
       </c>
       <c r="E30" t="n">
-        <v>4.6367901061919</v>
+        <v>2.012097318839147</v>
       </c>
       <c r="F30" t="n">
-        <v>4.323401815057131</v>
+        <v>5.413627307467223</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1631527133334464</v>
+        <v>0.08118031373748363</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2627670757132192</v>
+        <v>-0.5213534155119819</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6455359366496666</v>
+        <v>-0.7495236239530948</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6173551002934642</v>
+        <v>-0.7837331731648662</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.006747980082419597</v>
+        <v>-0.000628524660662909</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5722942505898675</v>
+        <v>-0.296244304008065</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.004022701233732184</v>
+        <v>-0.004905009984787212</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>65.24690094702329</v>
+        <v>93.6520910049601</v>
       </c>
       <c r="B31" t="n">
-        <v>111.2811199678033</v>
+        <v>160.4715786533601</v>
       </c>
       <c r="C31" t="n">
-        <v>45.93695491243493</v>
+        <v>45.67129417133599</v>
       </c>
       <c r="D31" t="n">
-        <v>11.94493160744152</v>
+        <v>9.088922196702738</v>
       </c>
       <c r="E31" t="n">
-        <v>2.76803304027643</v>
+        <v>2.029524804730301</v>
       </c>
       <c r="F31" t="n">
-        <v>5.95616760921161</v>
+        <v>9.76057356338266</v>
       </c>
       <c r="G31" t="n">
-        <v>0.05701238693668301</v>
+        <v>0.01513526705154798</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6876928243449153</v>
+        <v>-0.875449472017623</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8250197427508328</v>
+        <v>-0.9239491577812444</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8772211671302003</v>
+        <v>-0.9637390890745487</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.003256216285777143</v>
+        <v>-0.02455103556805395</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3623988997367757</v>
+        <v>-0.5422711484103406</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.001874537426059036</v>
+        <v>-0.01058152487679667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>46.0141356246277</v>
+        <v>98.48790237409939</v>
       </c>
       <c r="B32" t="n">
-        <v>83.75829331462758</v>
+        <v>73.09383791382821</v>
       </c>
       <c r="C32" t="n">
-        <v>45.92772581844063</v>
+        <v>45.72961753363473</v>
       </c>
       <c r="D32" t="n">
-        <v>8.94046436923318</v>
+        <v>8.707857284869322</v>
       </c>
       <c r="E32" t="n">
-        <v>2.633092969696345</v>
+        <v>2.454003843438309</v>
       </c>
       <c r="F32" t="n">
-        <v>4.117845096661388</v>
+        <v>10.57545433082196</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2006494313158181</v>
+        <v>0.01274135100738422</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1358806307258827</v>
+        <v>-0.8921883479136079</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5939682033063373</v>
+        <v>-0.9339742398707305</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5273180813845265</v>
+        <v>-0.9700354555857378</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.05495568299005416</v>
+        <v>-0.09589973965969925</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.5555367126034682</v>
+        <v>-0.5767263044154581</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0005424289055669301</v>
+        <v>-0.02391257911650999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>45.76248324189669</v>
+        <v>53.8530194580914</v>
       </c>
       <c r="B33" t="n">
-        <v>101.1917377867516</v>
+        <v>91.29961805938551</v>
       </c>
       <c r="C33" t="n">
-        <v>45.92457997357174</v>
+        <v>45.63415698605048</v>
       </c>
       <c r="D33" t="n">
-        <v>8.724794977298698</v>
+        <v>8.188957770615566</v>
       </c>
       <c r="E33" t="n">
-        <v>2.902027487495702</v>
+        <v>2.19106173443802</v>
       </c>
       <c r="F33" t="n">
-        <v>4.053314323192642</v>
+        <v>4.98973935347472</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2046869258577532</v>
+        <v>0.1076414875761806</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1219078675382372</v>
+        <v>-0.3789591306466633</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5884567130229917</v>
+        <v>-0.6930494053589055</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5171621731873152</v>
+        <v>-0.6957445927622061</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0001119051768554559</v>
+        <v>-0.04983445185790485</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5538657251841739</v>
+        <v>-0.5910691232345788</v>
       </c>
       <c r="M33" t="n">
-        <v>-8.836410174322869e-05</v>
+        <v>-0.002093025382967767</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>60.06313258305887</v>
+        <v>68.76201029089543</v>
       </c>
       <c r="B34" t="n">
-        <v>108.7689146913215</v>
+        <v>107.3640549626283</v>
       </c>
       <c r="C34" t="n">
-        <v>45.93734881394236</v>
+        <v>46.51823592733236</v>
       </c>
       <c r="D34" t="n">
-        <v>12.31944729636738</v>
+        <v>12.05378435333814</v>
       </c>
       <c r="E34" t="n">
-        <v>2.668482252776396</v>
+        <v>4.332048411234005</v>
       </c>
       <c r="F34" t="n">
-        <v>5.444986465102499</v>
+        <v>6.474831589654194</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07770928794501958</v>
+        <v>0.04609260494332986</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6015831699618376</v>
+        <v>-0.6934239248991461</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7850681930857725</v>
+        <v>-0.8276251014486635</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8303610830996451</v>
+        <v>-0.8803333668327037</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.000961781326319921</v>
+        <v>-0.03888898919694654</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.3345779284425775</v>
+        <v>-0.36492932332263</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.001931392362698124</v>
+        <v>-0.2041682119616818</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>81.98752781430143</v>
+        <v>61.86257492703567</v>
       </c>
       <c r="B35" t="n">
-        <v>82.86270701436943</v>
+        <v>169.5042407035486</v>
       </c>
       <c r="C35" t="n">
-        <v>45.92857654351899</v>
+        <v>45.63292572492849</v>
       </c>
       <c r="D35" t="n">
-        <v>10.36229016727508</v>
+        <v>12.73766973334425</v>
       </c>
       <c r="E35" t="n">
-        <v>2.567403812180721</v>
+        <v>4.429701905647004</v>
       </c>
       <c r="F35" t="n">
-        <v>8.000367146557112</v>
+        <v>5.699367650180754</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02465823733748387</v>
+        <v>0.06841560109239871</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8397811913678115</v>
+        <v>-0.58134863451883</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9034301667206833</v>
+        <v>-0.7757715261398507</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9493326295911885</v>
+        <v>-0.8189939946700029</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.07777621265698394</v>
+        <v>-0.01716809373761622</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.4874525497582566</v>
+        <v>-0.3157708463551291</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0006652208205899318</v>
+        <v>-0.001811594269369582</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>48.97233801325978</v>
+        <v>48.26654064396194</v>
       </c>
       <c r="B36" t="n">
-        <v>77.96180710643311</v>
+        <v>71.70205801578696</v>
       </c>
       <c r="C36" t="n">
-        <v>45.92495802156781</v>
+        <v>45.66284814540918</v>
       </c>
       <c r="D36" t="n">
-        <v>8.761421502977781</v>
+        <v>8.702618569809912</v>
       </c>
       <c r="E36" t="n">
-        <v>2.902027487495702</v>
+        <v>2.249157929086191</v>
       </c>
       <c r="F36" t="n">
-        <v>4.438695652882791</v>
+        <v>4.35812663251095</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1579933295054317</v>
+        <v>0.1633950940255794</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2816969856196778</v>
+        <v>-0.1441684052241615</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6532800991734175</v>
+        <v>-0.5977408288670859</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6303154453391854</v>
+        <v>-0.5345739044908312</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1040216552986578</v>
+        <v>-0.03410249634398486</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5751793598197864</v>
+        <v>-0.5637325141857525</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0001429307750302478</v>
+        <v>-0.008651004664955303</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>47.27280796770503</v>
+        <v>95.46734309109928</v>
       </c>
       <c r="B37" t="n">
-        <v>83.15222345921241</v>
+        <v>151.3187660017851</v>
       </c>
       <c r="C37" t="n">
-        <v>45.92817269145282</v>
+        <v>45.63371631400627</v>
       </c>
       <c r="D37" t="n">
-        <v>8.660123664605686</v>
+        <v>9.118454946424761</v>
       </c>
       <c r="E37" t="n">
-        <v>3.740464578808266</v>
+        <v>2.023549535543858</v>
       </c>
       <c r="F37" t="n">
-        <v>4.218023881823115</v>
+        <v>10.08774779868664</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1807021544837318</v>
+        <v>0.0141772030789374</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2025530585662308</v>
+        <v>-0.8821104132361356</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6208172392281825</v>
+        <v>-0.9278942726633893</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5752214044187212</v>
+        <v>-0.9662786739049737</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.03125052490719925</v>
+        <v>-0.08396079828332316</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.5638943749767439</v>
+        <v>-0.5552048195240824</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0006069296406856948</v>
+        <v>-0.00199230034429107</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>97.7665691485883</v>
+        <v>67.42466485010878</v>
       </c>
       <c r="B38" t="n">
-        <v>104.3233177565072</v>
+        <v>107.3640549626283</v>
       </c>
       <c r="C38" t="n">
-        <v>45.92838742300866</v>
+        <v>46.50154083271336</v>
       </c>
       <c r="D38" t="n">
-        <v>8.137057146507313</v>
+        <v>12.05188369719932</v>
       </c>
       <c r="E38" t="n">
-        <v>4.49880215695979</v>
+        <v>4.285815683723966</v>
       </c>
       <c r="F38" t="n">
-        <v>10.2863910129716</v>
+        <v>6.30213675966791</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01328159567039723</v>
+        <v>0.04954778868951265</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9034746374808206</v>
+        <v>-0.6752391503060239</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9409418742871423</v>
+        <v>-0.8189377334480666</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9740791720968285</v>
+        <v>-0.8708244148573961</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1183246789836912</v>
+        <v>-0.01585869941417304</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.6053230887969907</v>
+        <v>-0.355400737057025</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0006379235535586346</v>
+        <v>-0.2003521903344828</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>81.43379480354436</v>
+        <v>52.30996287098023</v>
       </c>
       <c r="B39" t="n">
-        <v>110.5211986403595</v>
+        <v>94.43030772926008</v>
       </c>
       <c r="C39" t="n">
-        <v>45.92801488987786</v>
+        <v>45.6641676244335</v>
       </c>
       <c r="D39" t="n">
-        <v>10.20553333379127</v>
+        <v>8.19869512256437</v>
       </c>
       <c r="E39" t="n">
-        <v>2.567403812180721</v>
+        <v>4.448565855225877</v>
       </c>
       <c r="F39" t="n">
-        <v>7.889793990385209</v>
+        <v>4.786368192640193</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02523931102927842</v>
+        <v>0.1201213891641298</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8366410241341955</v>
+        <v>-0.3231962374347478</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9016923800933863</v>
+        <v>-0.6706990669341446</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9480169716801173</v>
+        <v>-0.6589154972502229</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.03558522380285904</v>
+        <v>-0.002390122002908928</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4833161255561313</v>
+        <v>-0.5812964315162081</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.0005841528846283103</v>
+        <v>-0.008952599870512973</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>76.4313074852208</v>
+        <v>46.44006120956742</v>
       </c>
       <c r="B40" t="n">
-        <v>120.7403708182446</v>
+        <v>71.70205801578696</v>
       </c>
       <c r="C40" t="n">
-        <v>45.96118569773565</v>
+        <v>45.6319913934985</v>
       </c>
       <c r="D40" t="n">
-        <v>10.81528959681478</v>
+        <v>8.701887503482975</v>
       </c>
       <c r="E40" t="n">
-        <v>4.243862744467455</v>
+        <v>2.349243126759788</v>
       </c>
       <c r="F40" t="n">
-        <v>7.252968166105692</v>
+        <v>4.139667159746619</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03175886749702561</v>
+        <v>0.1893285921071974</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8035415127247094</v>
+        <v>-0.04041807378216037</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8835850858968715</v>
+        <v>-0.5569934843450017</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9336199616392059</v>
+        <v>-0.4580891612375234</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.03160890253344189</v>
+        <v>-0.0143862693559357</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.445947196465112</v>
+        <v>-0.5596004080637829</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.004774188344076721</v>
+        <v>-0.001598032799655924</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>93.0283639015373</v>
+        <v>48.98666920552276</v>
       </c>
       <c r="B41" t="n">
-        <v>84.6367516057781</v>
+        <v>69.21831974190323</v>
       </c>
       <c r="C41" t="n">
-        <v>45.9276620210675</v>
+        <v>45.63930428882482</v>
       </c>
       <c r="D41" t="n">
-        <v>8.644821803641275</v>
+        <v>8.497685639764017</v>
       </c>
       <c r="E41" t="n">
-        <v>2.776490273608517</v>
+        <v>2.965601322123918</v>
       </c>
       <c r="F41" t="n">
-        <v>9.524465563659389</v>
+        <v>4.411726573115941</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01575609067124117</v>
+        <v>0.1542780089140406</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8887554087892674</v>
+        <v>-0.1810353410606771</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9319360047457971</v>
+        <v>-0.6125444341458181</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9687342999560252</v>
+        <v>-0.561057048173119</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.05571838943170673</v>
+        <v>-0.04812099293585956</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.5699283652067504</v>
+        <v>-0.5765777947034851</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0005332205234241087</v>
+        <v>-0.003269551731387987</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>78.51830799639281</v>
+        <v>46.32050234326326</v>
       </c>
       <c r="B42" t="n">
-        <v>119.5879855040237</v>
+        <v>71.61932749338517</v>
       </c>
       <c r="C42" t="n">
-        <v>45.95651697658366</v>
+        <v>45.63521807657308</v>
       </c>
       <c r="D42" t="n">
-        <v>11.465144517913</v>
+        <v>8.657408752299387</v>
       </c>
       <c r="E42" t="n">
-        <v>2.666172279521859</v>
+        <v>2.233108979433326</v>
       </c>
       <c r="F42" t="n">
-        <v>7.662731846235038</v>
+        <v>4.118524428259794</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02892507956433161</v>
+        <v>0.1911636798466279</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8181769856873571</v>
+        <v>-0.03307722057853869</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8914096249009484</v>
+        <v>-0.5541602126984244</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9400751847707169</v>
+        <v>-0.4525743379970841</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.1788594498429515</v>
+        <v>-0.0006348681127487231</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4615372358099881</v>
+        <v>-0.5588033489550883</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.004229042975204767</v>
+        <v>-0.002335560359561367</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47.8563082819657</v>
+        <v>69.71449985184232</v>
       </c>
       <c r="B43" t="n">
-        <v>87.3291015917054</v>
+        <v>88.92023753026936</v>
       </c>
       <c r="C43" t="n">
-        <v>45.96118569773565</v>
+        <v>45.65806203595591</v>
       </c>
       <c r="D43" t="n">
-        <v>8.481851756614763</v>
+        <v>11.97103447332021</v>
       </c>
       <c r="E43" t="n">
-        <v>4.243862744467455</v>
+        <v>2.046458235621583</v>
       </c>
       <c r="F43" t="n">
-        <v>4.258826867040034</v>
+        <v>6.548214410022079</v>
       </c>
       <c r="G43" t="n">
-        <v>0.172282973290063</v>
+        <v>0.04374313211881947</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2311532650747002</v>
+        <v>-0.7085833365927411</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6325154827763513</v>
+        <v>-0.8360753895935584</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.5953767769680417</v>
+        <v>-0.8884604573031646</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.009408201702045212</v>
+        <v>-0.0872455891808557</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5677688532300499</v>
+        <v>-0.3978587488888173</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.004774188344076721</v>
+        <v>-0.007557036789923588</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>46.97234257325533</v>
+        <v>76.18801717860825</v>
       </c>
       <c r="B44" t="n">
-        <v>87.73232370517813</v>
+        <v>80.35915222076871</v>
       </c>
       <c r="C44" t="n">
-        <v>45.92880343116914</v>
+        <v>45.68017708130154</v>
       </c>
       <c r="D44" t="n">
-        <v>8.657051193179758</v>
+        <v>10.93003718608782</v>
       </c>
       <c r="E44" t="n">
-        <v>4.359002557728287</v>
+        <v>2.12327352102966</v>
       </c>
       <c r="F44" t="n">
-        <v>4.182212474682138</v>
+        <v>7.268149496610171</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1851591579746675</v>
+        <v>0.03150133043834263</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1873419988099723</v>
+        <v>-0.7753015140057881</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.614653985345482</v>
+        <v>-0.8694873774254431</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.564415582292945</v>
+        <v>-0.9209905249818473</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02141476696738852</v>
+        <v>-0.04704233324038298</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.561899266134101</v>
+        <v>-0.4464101288395619</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0006979693192114296</v>
+        <v>-0.01261190429749551</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>62.72508948483475</v>
+        <v>66.71030480453378</v>
       </c>
       <c r="B45" t="n">
-        <v>108.7689146913215</v>
+        <v>169.5042407035486</v>
       </c>
       <c r="C45" t="n">
-        <v>45.93734881394236</v>
+        <v>47.03598629883295</v>
       </c>
       <c r="D45" t="n">
-        <v>12.31944729636738</v>
+        <v>12.07907820922935</v>
       </c>
       <c r="E45" t="n">
-        <v>2.469484967832142</v>
+        <v>2.149773178860499</v>
       </c>
       <c r="F45" t="n">
-        <v>5.716130562544524</v>
+        <v>6.2396206154149</v>
       </c>
       <c r="G45" t="n">
-        <v>0.06617938731442356</v>
+        <v>0.05158796767202935</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.6491747381073665</v>
+        <v>-0.6648378654422484</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8067897778524622</v>
+        <v>-0.8139946509219185</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.856705229542294</v>
+        <v>-0.8652953788320938</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01993187808193474</v>
+        <v>-0.0195124469710351</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.3435607922684645</v>
+        <v>-0.3503109217323032</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.001931392362698124</v>
+        <v>-0.3225111540189611</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>71.82587102021159</v>
+        <v>49.03390006347704</v>
       </c>
       <c r="B46" t="n">
-        <v>128.2490475721308</v>
+        <v>69.8854928193346</v>
       </c>
       <c r="C46" t="n">
-        <v>46.18486670770949</v>
+        <v>45.63930428882482</v>
       </c>
       <c r="D46" t="n">
-        <v>11.23915512624308</v>
+        <v>8.497685639764017</v>
       </c>
       <c r="E46" t="n">
-        <v>4.979527330341602</v>
+        <v>2.175270453528961</v>
       </c>
       <c r="F46" t="n">
-        <v>6.693278862439305</v>
+        <v>4.417544294505932</v>
       </c>
       <c r="G46" t="n">
-        <v>0.03988530715323109</v>
+        <v>0.1537132307566207</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.7644276402718347</v>
+        <v>-0.183370927302057</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8630700880634523</v>
+        <v>-0.6134865686161551</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9155502352219899</v>
+        <v>-0.5627204392661502</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.01398954762833061</v>
+        <v>-0.01043467918250661</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.4115442649346832</v>
+        <v>-0.5687203504126008</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0202976119031434</v>
+        <v>-0.003269551731387987</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>65.53640401574471</v>
+        <v>62.73897817100479</v>
       </c>
       <c r="B47" t="n">
-        <v>103.41412381365</v>
+        <v>169.5042407035486</v>
       </c>
       <c r="C47" t="n">
-        <v>45.95854943873726</v>
+        <v>45.63225759030087</v>
       </c>
       <c r="D47" t="n">
-        <v>11.93539721340784</v>
+        <v>12.73766973334425</v>
       </c>
       <c r="E47" t="n">
-        <v>4.564675565905345</v>
+        <v>2.599057429434591</v>
       </c>
       <c r="F47" t="n">
-        <v>5.990941787589964</v>
+        <v>5.802256723795724</v>
       </c>
       <c r="G47" t="n">
-        <v>0.05608276019566028</v>
+        <v>0.06491311533725636</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6917240583516399</v>
+        <v>-0.5983468238205304</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8269529322836792</v>
+        <v>-0.783372016384025</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8793198675262948</v>
+        <v>-0.8286889179726105</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.007370654100285717</v>
+        <v>-0.03054522733480262</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.3645615078471565</v>
+        <v>-0.3220152194684092</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.004466364351738236</v>
+        <v>-0.001658877783056734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>53.97099384381805</v>
+        <v>74.1683290142454</v>
       </c>
       <c r="B48" t="n">
-        <v>100.2894987822851</v>
+        <v>158.8336275493536</v>
       </c>
       <c r="C48" t="n">
-        <v>45.92768317499728</v>
+        <v>45.63519003592157</v>
       </c>
       <c r="D48" t="n">
-        <v>7.958832057502728</v>
+        <v>11.3764098784794</v>
       </c>
       <c r="E48" t="n">
-        <v>4.550348780164553</v>
+        <v>2.397084540500772</v>
       </c>
       <c r="F48" t="n">
-        <v>4.948111055507165</v>
+        <v>7.053507433371371</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1089289454094386</v>
+        <v>0.03478983226730051</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.4614756590540049</v>
+        <v>-0.7546453540382746</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7266879435810397</v>
+        <v>-0.857998913392195</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.7479437186977845</v>
+        <v>-0.9109764680127096</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.09485479588102862</v>
+        <v>-0.004074827705451701</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.6083707443622247</v>
+        <v>-0.4034493442264984</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0005362738383126767</v>
+        <v>-0.002329151067788499</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48.04177095328843</v>
+        <v>59.10439141478845</v>
       </c>
       <c r="B49" t="n">
-        <v>84.20269298484756</v>
+        <v>163.2311148534781</v>
       </c>
       <c r="C49" t="n">
-        <v>45.95474982949233</v>
+        <v>45.64614751622649</v>
       </c>
       <c r="D49" t="n">
-        <v>8.574443022260061</v>
+        <v>12.89551986353864</v>
       </c>
       <c r="E49" t="n">
-        <v>4.6367901061919</v>
+        <v>2.031242225670397</v>
       </c>
       <c r="F49" t="n">
-        <v>4.296118725007532</v>
+        <v>5.411455983705075</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1698344942354295</v>
+        <v>0.08127069514310033</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2398424572523018</v>
+        <v>-0.5209330488652996</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6360667045129982</v>
+        <v>-0.7493433867203875</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.6014328321719602</v>
+        <v>-0.7834809074284904</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03627975208540114</v>
+        <v>-0.0001766884429625355</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5690003368630114</v>
+        <v>-0.2961187888303677</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.004022701233732184</v>
+        <v>-0.004833717994627007</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>89.39798797213905</v>
+        <v>74.09072182504106</v>
       </c>
       <c r="B50" t="n">
-        <v>110.1112289829704</v>
+        <v>95.26953904812893</v>
       </c>
       <c r="C50" t="n">
-        <v>45.94358484087903</v>
+        <v>45.63504995648469</v>
       </c>
       <c r="D50" t="n">
-        <v>9.061734404182472</v>
+        <v>11.38676796581935</v>
       </c>
       <c r="E50" t="n">
-        <v>4.690408699493172</v>
+        <v>2.357137771273627</v>
       </c>
       <c r="F50" t="n">
-        <v>8.974245587583201</v>
+        <v>7.044359267446966</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01810242146892701</v>
+        <v>0.03492391967305079</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8752843066734168</v>
+        <v>-0.7538907561842118</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9238896926315581</v>
+        <v>-0.8576145309430163</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9636339735013212</v>
+        <v>-0.91061296177855</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.02711847221697751</v>
+        <v>-0.00439751548904508</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.5428092038682484</v>
+        <v>-0.4028963930034175</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.002719016212096867</v>
+        <v>-0.002297132910786676</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>52.09482530030908</v>
+        <v>77.25778511921179</v>
       </c>
       <c r="B51" t="n">
-        <v>93.22406177174494</v>
+        <v>173.8840033654808</v>
       </c>
       <c r="C51" t="n">
-        <v>45.92991013517072</v>
+        <v>45.63563030485773</v>
       </c>
       <c r="D51" t="n">
-        <v>8.003008265809147</v>
+        <v>11.68706662516019</v>
       </c>
       <c r="E51" t="n">
-        <v>4.24049264111354</v>
+        <v>2.129045078341478</v>
       </c>
       <c r="F51" t="n">
-        <v>4.707239400784945</v>
+        <v>7.545476769906264</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1245117629076513</v>
+        <v>0.03007564562496415</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4021467591116413</v>
+        <v>-0.7820897276346372</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7024872693266033</v>
+        <v>-0.8720928892480707</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.7103997218673966</v>
+        <v>-0.92391940840751</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.03794178063294072</v>
+        <v>-0.1121914196589316</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5959128689443289</v>
+        <v>-0.425461718974384</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0008577087076148394</v>
+        <v>-0.002429783967480559</v>
       </c>
     </row>
   </sheetData>
